--- a/src/attributions/attributions_ig_traj_206.xlsx
+++ b/src/attributions/attributions_ig_traj_206.xlsx
@@ -1571,19 +1571,19 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2029285906775732</v>
+        <v>0.3057523227460114</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0489198425369044</v>
+        <v>0.06579167629790363</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2039069797821435</v>
+        <v>-0.2601915802061966</v>
       </c>
       <c r="G3" t="n">
         <v>-0</v>
@@ -1592,55 +1592,55 @@
         <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01382290575525684</v>
+        <v>0.02968277776807611</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002449478488282985</v>
+        <v>0.005423304434093882</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0442631625800613</v>
+        <v>0.04831272363754007</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01211027083294388</v>
+        <v>-0.1222037196172892</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.08874809981403427</v>
+        <v>-0.09282947229337751</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.03943152316872708</v>
+        <v>-0.1350358918814083</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" t="n">
         <v>-0</v>
@@ -1649,22 +1649,22 @@
         <v>-0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.03112777673599575</v>
+        <v>0.119718367081547</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1204441421551671</v>
+        <v>0.05716150181979567</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.04790809052615605</v>
+        <v>0.1472858053044284</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
@@ -1673,40 +1673,40 @@
         <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.04818484970019409</v>
+        <v>0.120955653445357</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.04277794525325546</v>
+        <v>-0.05564058727457193</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.1195547718489098</v>
+        <v>-0.2355049025935752</v>
       </c>
       <c r="AQ3" t="n">
         <v>-0</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.2433553909377797</v>
+        <v>0.6427071852819255</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1715,25 +1715,25 @@
         <v>-0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.1476706980403516</v>
+        <v>-0.2523550040367366</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.3810584717826482</v>
+        <v>-0.4216575468079953</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.1207749947031511</v>
+        <v>0.1128562629496318</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
@@ -1742,13 +1742,13 @@
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.02615956116734798</v>
+        <v>0.06564242316416113</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0.06621391016378995</v>
+        <v>-0.1645604742129381</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
         <v>-0</v>
@@ -1757,76 +1757,76 @@
         <v>-0</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.0001840758772916465</v>
+        <v>0.06596592720487399</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.02701159701704657</v>
+        <v>0.08780911047235011</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.01590446965451614</v>
+        <v>0.1642245428998055</v>
       </c>
       <c r="BR3" t="n">
         <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.06387948538210578</v>
+        <v>0.2162555667136201</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.1019661637218371</v>
+        <v>-0.102726014258895</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.1161547233751528</v>
+        <v>-0.2776585600512539</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB3" t="n">
         <v>-0</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD3" t="n">
         <v>-0</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.09999892273220937</v>
+        <v>-0.2562667729184678</v>
       </c>
       <c r="CF3" t="n">
         <v>0</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.02256445087727526</v>
+        <v>-0.06093926397851217</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.1114156746813355</v>
+        <v>0.1766194307047158</v>
       </c>
       <c r="CJ3" t="n">
         <v>0</v>
@@ -1835,58 +1835,58 @@
         <v>0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
         <v>0</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.002618536853996481</v>
+        <v>-0.233475686560081</v>
       </c>
       <c r="CO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP3" t="n">
         <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.04480032653624928</v>
+        <v>0.05658685757637985</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.01230190190511231</v>
+        <v>0.143933765759135</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW3" t="n">
-        <v>-0.08135667542982904</v>
+        <v>-0.2446523429804898</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY3" t="n">
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.01477688769894233</v>
+        <v>-0.05575568320706113</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.1251135891169797</v>
+        <v>0.1517969809323543</v>
       </c>
       <c r="DB3" t="n">
         <v>-0</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD3" t="n">
         <v>0</v>
@@ -1895,73 +1895,73 @@
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.04869346391191082</v>
+        <v>-0.1324954261874808</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.04670034693943906</v>
+        <v>-0.05048531141379477</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.004921230597223906</v>
+        <v>0.1371458580937623</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.0170690965166942</v>
+        <v>-0.08674429709316184</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.09762799927350577</v>
+        <v>0.007552348485462051</v>
       </c>
       <c r="DS3" t="n">
-        <v>-0.01651112157121482</v>
+        <v>0.07261903360331157</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.04786376305129841</v>
+        <v>0.159260147069458</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ3" t="n">
         <v>0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.002466107036125797</v>
+        <v>-0.04484137452983293</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.01062321062650451</v>
+        <v>0.1673148913369745</v>
       </c>
       <c r="EC3" t="n">
         <v>-0</v>
@@ -1973,25 +1973,25 @@
         <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.1072336276855924</v>
+        <v>-0.1198412885971141</v>
       </c>
       <c r="EH3" t="n">
         <v>0</v>
       </c>
       <c r="EI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.01160921830577171</v>
+        <v>-0.0864650391803147</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.1230465486167455</v>
+        <v>0.153367871689946</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM3" t="n">
         <v>-0</v>
@@ -2000,10 +2000,10 @@
         <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0.04786519836445473</v>
+        <v>-0.1693119702494127</v>
       </c>
       <c r="EQ3" t="n">
         <v>-0</v>
@@ -2012,37 +2012,37 @@
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.03713622642471926</v>
+        <v>-0.1895854796273398</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.06123291785697746</v>
+        <v>0.1621745883383629</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW3" t="n">
         <v>-0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.08002683643796135</v>
+        <v>-0.2347041410654898</v>
       </c>
       <c r="EZ3" t="n">
         <v>-0</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.02696689249196997</v>
+        <v>-0.1166271024937341</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.1144545931797553</v>
+        <v>0.1609001969343876</v>
       </c>
       <c r="FD3" t="n">
         <v>0</v>
@@ -2054,22 +2054,22 @@
         <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0.07328578524471889</v>
+        <v>-0.1241926100016105</v>
       </c>
       <c r="FI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ3" t="n">
         <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.05502268613446842</v>
+        <v>-0.07009745179052719</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.128991699199469</v>
+        <v>0.2878688561545821</v>
       </c>
       <c r="FM3" t="n">
         <v>0</v>
@@ -2081,58 +2081,58 @@
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>-0.1536573435632627</v>
+        <v>-0.008678678164605866</v>
       </c>
       <c r="FR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS3" t="n">
         <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.04836743607576374</v>
+        <v>0.06419936475337053</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.07015484150652893</v>
+        <v>0.05834805540727327</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0.04359163589180996</v>
+        <v>-0.1165236057022418</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB3" t="n">
         <v>0</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0.02660780921729116</v>
+        <v>0.1928152609455519</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -2706,10 +2706,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.06164528477532262</v>
+        <v>0.3723447833601671</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -2718,25 +2718,25 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.00947181562570072</v>
+        <v>0.03270131570441095</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.02084134091931661</v>
+        <v>-0.1481132587545465</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008402246568090087</v>
+        <v>0.07806574086418649</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2745,43 +2745,43 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.001642007652415226</v>
+        <v>-0.0123789304044336</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.005576725341241475</v>
+        <v>-0.0474207524753178</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002505032973461024</v>
+        <v>0.1531175198803662</v>
       </c>
       <c r="U5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.006786407708217594</v>
+        <v>-0.1393495340047074</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001086050619200524</v>
+        <v>-0.03251322459877232</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -2790,79 +2790,79 @@
         <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.0118166067507868</v>
+        <v>0.02668232532783662</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.02381388958612998</v>
+        <v>-0.2318199362577361</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.0008413102544217923</v>
+        <v>0.03641095460051185</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
         <v>-0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.003161421802135167</v>
+        <v>0.2001752736061113</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.01248545679290628</v>
+        <v>0.1517265925466987</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.01638385987357694</v>
+        <v>-0.14776295440619</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
         <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
         <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.08167188550284556</v>
+        <v>0.7523265048028468</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.002983426838779252</v>
+        <v>-0.2236557542142625</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.005011874375008684</v>
+        <v>-0.1946416528082396</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB5" t="n">
         <v>0</v>
@@ -2871,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.03076870170503649</v>
+        <v>-0.02013384261836163</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,25 +2880,25 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.02042812232900237</v>
+        <v>-0.07032665556398773</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.04950450233859762</v>
+        <v>-0.1123049925139021</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
         <v>-0</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.03339932611301159</v>
+        <v>0.03469309981712113</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
@@ -2907,13 +2907,13 @@
         <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.02317441788268359</v>
+        <v>0.1329383957358534</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.004460504489089329</v>
+        <v>0.157470095687143</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,7 +2925,7 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.0286586207638927</v>
+        <v>0.3829288205992971</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
@@ -2934,43 +2934,43 @@
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.006181886832478472</v>
+        <v>-0.02554702847301625</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.003962433757637929</v>
+        <v>-0.2462874241705843</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.01835562934276924</v>
+        <v>-0.2470015968941225</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
         <v>0</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.001471314198837709</v>
+        <v>-0.03765293856164183</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.01874654599405379</v>
+        <v>0.1688854066205257</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL5" t="n">
         <v>0</v>
@@ -2979,49 +2979,49 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.008115025392112053</v>
+        <v>-0.1605812045751217</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
         <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.003892852275518035</v>
+        <v>0.0877320112976422</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.0007763791134900563</v>
+        <v>-0.0004823473311048004</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT5" t="n">
         <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.01397064473119442</v>
+        <v>-0.2229940873196077</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>-0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.003277750691518288</v>
+        <v>-0.0318494895672547</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.01864369185728248</v>
+        <v>0.1684761980209558</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC5" t="n">
         <v>0</v>
@@ -3033,52 +3033,52 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.004083767682804701</v>
+        <v>-0.0382963263445471</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH5" t="n">
         <v>-0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.02423368004716522</v>
+        <v>-0.07715113876007045</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.003587403050199469</v>
+        <v>0.0391536105044364</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.003631185777059407</v>
+        <v>-0.1060452160158828</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>2.829028960275197e-05</v>
+        <v>-0.002280503920621933</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.005105422811569684</v>
+        <v>0.0101241945769894</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>-0</v>
@@ -3087,46 +3087,46 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.01291134167828595</v>
+        <v>0.09279946202944754</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.03098297264176144</v>
+        <v>-0.07920632051252594</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.000508662513114477</v>
+        <v>0.1261248261701846</v>
       </c>
       <c r="EC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.01563837895745484</v>
+        <v>-0.05020222813408409</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI5" t="n">
         <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.0004256991142169907</v>
+        <v>-0.1450857324674949</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.01133111537309056</v>
+        <v>0.08032194995051321</v>
       </c>
       <c r="EL5" t="n">
         <v>-0</v>
@@ -3138,10 +3138,10 @@
         <v>0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.01844991367882736</v>
+        <v>-0.1307088247943847</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
@@ -3150,37 +3150,37 @@
         <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.009148878918307549</v>
+        <v>-0.2127589826205118</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.005591449427534576</v>
+        <v>0.03934420998924418</v>
       </c>
       <c r="EU5" t="n">
         <v>0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
         <v>0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.01719665210809002</v>
+        <v>-0.2461501097544718</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA5" t="n">
         <v>0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.004086736241996445</v>
+        <v>-0.07529357539274659</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.01990846078849886</v>
+        <v>0.1444772395630748</v>
       </c>
       <c r="FD5" t="n">
         <v>0</v>
@@ -3189,13 +3189,13 @@
         <v>-0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.001370416529415584</v>
+        <v>-0.2097378547464279</v>
       </c>
       <c r="FI5" t="n">
         <v>0</v>
@@ -3204,67 +3204,67 @@
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.02718747500816612</v>
+        <v>0.07689302414421577</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.01927846596110732</v>
+        <v>0.2473284011354092</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.001412926287801983</v>
+        <v>-0.02881714120084175</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0003343553842685277</v>
+        <v>-0.0008173531966460252</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.008361267083601616</v>
+        <v>0.1080102913238926</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.02668185660748199</v>
+        <v>-0.09812784982167637</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
         <v>-0</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.006945079661175605</v>
+        <v>0.1019689153658571</v>
       </c>
       <c r="GE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF5" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1191637788464301</v>
+        <v>0.3778613044784142</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3287,13 +3287,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.000244472505624229</v>
+        <v>0.02849207907819654</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0775106720181679</v>
+        <v>-0.1836100948352341</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H6" t="n">
         <v>-0</v>
@@ -3305,7 +3305,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03302838053058574</v>
+        <v>0.1455419169676797</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0002387669203468907</v>
+        <v>-0.01419360066480611</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.03003977676142359</v>
+        <v>-0.07765334978164609</v>
       </c>
       <c r="P6" t="n">
         <v>-0</v>
@@ -3329,10 +3329,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.002284935655014759</v>
+        <v>0.1180120793323559</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3341,37 +3341,37 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.02285615139674775</v>
+        <v>-0.151815996269272</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.002035207997721834</v>
+        <v>-0.0286213852713408</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.01466475381318209</v>
+        <v>0.05242708817068826</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.02499733283907983</v>
+        <v>-0.2346623093466465</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.003625874880884475</v>
+        <v>-0.08678582768483063</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
@@ -3386,22 +3386,22 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.02024443533119928</v>
+        <v>0.1676093115223271</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.002488386176331627</v>
+        <v>0.1079944240206459</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.03683754671665188</v>
+        <v>-0.1103329200769282</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
         <v>-0</v>
@@ -3410,22 +3410,22 @@
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.1278014506336576</v>
+        <v>0.6652669174793525</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.01175623674190871</v>
+        <v>-0.1650130555279703</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.0900154314256542</v>
+        <v>-0.1918088033585739</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -3440,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.05362211914798582</v>
+        <v>-0.005390590819121107</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,40 +3449,40 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.03211875218902337</v>
+        <v>-0.03662852657117052</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.06676288011334312</v>
+        <v>-0.1576517212884833</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.04458169923675846</v>
+        <v>0.04910847126916346</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.02126862868062271</v>
+        <v>0.08784564411504185</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0.007043322162713457</v>
+        <v>0.05081774320523187</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>0</v>
@@ -3491,10 +3491,10 @@
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.04455691860171433</v>
+        <v>0.3173876833650052</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,13 +3503,13 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.003401293739031888</v>
+        <v>-0.0396185754647539</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.02467392885279949</v>
+        <v>-0.1429860922838909</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>-0</v>
@@ -3521,22 +3521,22 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.03511691291232748</v>
+        <v>-0.2230112104191768</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.004431916780775235</v>
+        <v>-0.03824753962087318</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.03606415395618955</v>
+        <v>0.1375414661742255</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
@@ -3548,73 +3548,73 @@
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.004074752419878877</v>
+        <v>-0.133468630610159</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.009724712516633186</v>
+        <v>0.04810326481924673</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.003520570998939234</v>
+        <v>0.007859435166270499</v>
       </c>
       <c r="CS6" t="n">
         <v>-0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
         <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.03046445154678787</v>
+        <v>-0.2045450286298391</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
         <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.0002365190742413883</v>
+        <v>-0.0352503407690993</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.03887609900341878</v>
+        <v>0.1461433650845621</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
         <v>-0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.01034247757987183</v>
+        <v>-0.05932880938322233</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.00813141640399475</v>
+        <v>-0.04206817422686795</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.005290865928317907</v>
+        <v>0.03767508732298684</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3626,28 +3626,28 @@
         <v>0</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.01676601883045015</v>
+        <v>-0.1202276270456558</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.01100865933635951</v>
+        <v>-0.01570233707490479</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0.008103463346265306</v>
+        <v>0.06758872960097351</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
         <v>-0</v>
@@ -3656,19 +3656,19 @@
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.0129492763358943</v>
+        <v>0.02613499014974608</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.02228210556374816</v>
+        <v>0.09186621841830427</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.001582632522033156</v>
+        <v>0.1407803128045796</v>
       </c>
       <c r="EC6" t="n">
         <v>-0</v>
@@ -3677,28 +3677,28 @@
         <v>-0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
         <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.0247554421519228</v>
+        <v>-0.04287318118774365</v>
       </c>
       <c r="EH6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI6" t="n">
         <v>0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.000471459209142786</v>
+        <v>-0.08342510944347767</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.02826041639991656</v>
+        <v>0.05427385247179062</v>
       </c>
       <c r="EL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
         <v>-0</v>
@@ -3707,28 +3707,28 @@
         <v>0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.02713202593662809</v>
+        <v>-0.1114991590851256</v>
       </c>
       <c r="EQ6" t="n">
         <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.005385721609663822</v>
+        <v>-0.08860508754012039</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.03309245763536544</v>
+        <v>0.07296839794279883</v>
       </c>
       <c r="EU6" t="n">
         <v>0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
         <v>0</v>
@@ -3737,34 +3737,34 @@
         <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.02705060628418314</v>
+        <v>-0.2268161139609564</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA6" t="n">
         <v>-0</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.002302468110360555</v>
+        <v>-0.05892538329875015</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.03650115454140639</v>
+        <v>0.1276088596143859</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
         <v>0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.007137900638944977</v>
+        <v>-0.2431237035835043</v>
       </c>
       <c r="FI6" t="n">
         <v>0</v>
@@ -3773,64 +3773,64 @@
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.0255698564969661</v>
+        <v>0.07942028805398021</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.01900989711617514</v>
+        <v>0.2388403238926852</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO6" t="n">
         <v>0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.005737293127769899</v>
+        <v>-0.0343818719065719</v>
       </c>
       <c r="FR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS6" t="n">
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.001099278822622304</v>
+        <v>-0.006156833086654549</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.02910416436813578</v>
+        <v>0.136569411252558</v>
       </c>
       <c r="FV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.02102059787942549</v>
+        <v>-0.04978062805638354</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.004307472663903668</v>
+        <v>0.02158113824724713</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
@@ -4416,154 +4416,154 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2237328732943498</v>
+        <v>0.5915928228725817</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.06515417034618702</v>
+        <v>-0.02703904971993809</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.04925240757766072</v>
+        <v>0.08599319928904407</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.08476463419001774</v>
+        <v>-0.237825335095307</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.113946609723205</v>
+        <v>0.4477958636757286</v>
       </c>
       <c r="L8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.04348223548823189</v>
+        <v>-0.115732078472011</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.02053297659647814</v>
+        <v>-0.02416591850882351</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.03670406915433636</v>
+        <v>-0.09670599751248868</v>
       </c>
       <c r="P8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.04947635697741309</v>
+        <v>0.1672337308926944</v>
       </c>
       <c r="U8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.0155026513131434</v>
+        <v>-0.1730801486147821</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03229165502607485</v>
+        <v>-0.1562992695118425</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0278265653086327</v>
+        <v>0.006167786015266592</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.01191232362629384</v>
+        <v>0.1326823582750994</v>
       </c>
       <c r="AD8" t="n">
         <v>-0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.04625124271083816</v>
+        <v>-0.3583078217787987</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.007114254808101944</v>
+        <v>-0.232765192223638</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.0261174273394349</v>
+        <v>-0.1208615506671584</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.002666214520989679</v>
+        <v>0.2796811097213507</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.03086087095530536</v>
+        <v>-0.1420132545468101</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.02184178988213995</v>
+        <v>0.1855140622374054</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.03432867370494121</v>
+        <v>-0.1993903488538412</v>
       </c>
       <c r="AQ8" t="n">
         <v>-0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.3227150389750425</v>
+        <v>0.864545694427319</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0.007751379962732096</v>
+        <v>-0.009316265426709647</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0526009955330097</v>
+        <v>-0.1689379298351239</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.04119718507186194</v>
+        <v>-0.1561617112762206</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
@@ -4572,58 +4572,58 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.03383296358613373</v>
+        <v>0.01679503937030948</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.04651532443530802</v>
+        <v>-0.1072122271818247</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.08118682525031878</v>
+        <v>-0.125129144069843</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.1414536344066122</v>
+        <v>-0.2593369916515429</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
         <v>-0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.07632378989844175</v>
+        <v>0.04420871583938941</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.04455902229673983</v>
+        <v>0.003950810730606918</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.07446637399510551</v>
+        <v>0.1409970762303681</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.01559255748328089</v>
+        <v>0.01292197288663296</v>
       </c>
       <c r="BR8" t="n">
         <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT8" t="n">
         <v>0</v>
@@ -4632,19 +4632,19 @@
         <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.1145850201877866</v>
+        <v>0.401924531779132</v>
       </c>
       <c r="BW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.02824704025963684</v>
+        <v>-0.09813528066541953</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.01016993953042968</v>
+        <v>0.003017374006007177</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.02534765932683216</v>
+        <v>-0.1821313840544908</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
@@ -4653,28 +4653,28 @@
         <v>-0</v>
       </c>
       <c r="CC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.05771564292045581</v>
+        <v>-0.2894894678529111</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.004502205442877549</v>
+        <v>0.05270337809803905</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.002437689983302286</v>
+        <v>-0.07350026865210699</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.04911678631156369</v>
+        <v>0.129299637004917</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
@@ -4683,109 +4683,109 @@
         <v>0</v>
       </c>
       <c r="CM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.02310077433991674</v>
+        <v>-0.2036905910701229</v>
       </c>
       <c r="CO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>-0.03296701065330334</v>
+        <v>0.1596578862146527</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.03164894325336205</v>
+        <v>0.0184589665216395</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.02088150581299981</v>
+        <v>0.0973130588115652</v>
       </c>
       <c r="CS8" t="n">
         <v>0</v>
       </c>
       <c r="CT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
         <v>-0</v>
       </c>
       <c r="CV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.04980342204901105</v>
+        <v>-0.2651658720770109</v>
       </c>
       <c r="CX8" t="n">
         <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.02205934984653552</v>
+        <v>0.06204277344703473</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.002858505550361955</v>
+        <v>-0.08647788939643147</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0546092542740864</v>
+        <v>0.1277375875281912</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.01221774180187424</v>
+        <v>-0.04667460133478842</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.07270909583350729</v>
+        <v>-0.01751025877837298</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0.01725989780393908</v>
+        <v>0.4670989354918933</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.005452412780540087</v>
+        <v>0.02414726860203964</v>
       </c>
       <c r="DK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL8" t="n">
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
         <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.02989548832981614</v>
+        <v>-0.1022234194423413</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.02975168509669514</v>
+        <v>0.05996840912381157</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.016942381946406</v>
+        <v>-0.1070851832848327</v>
       </c>
       <c r="DS8" t="n">
-        <v>-0.02395800829112853</v>
+        <v>0.1413922389906969</v>
       </c>
       <c r="DT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
         <v>-0</v>
@@ -4794,190 +4794,190 @@
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.01547217220507177</v>
+        <v>0.1552462539458248</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>-0.0003033135218409532</v>
+        <v>0.07858529855686996</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.03729696935685564</v>
+        <v>-0.01287561130452411</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.004443582272796644</v>
+        <v>-0.01919168053910613</v>
       </c>
       <c r="EC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.09215359024793898</v>
+        <v>-0.1240083848895802</v>
       </c>
       <c r="EH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.0357190691668179</v>
+        <v>0.08235209679429548</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.03803058930497912</v>
+        <v>-0.1113750297866926</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.01388623117169927</v>
+        <v>-0.03174695355072726</v>
       </c>
       <c r="EL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.03423827687995525</v>
+        <v>-0.1218329449272588</v>
       </c>
       <c r="EQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.005051869266449025</v>
+        <v>-0.06315923786977995</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.00201055681616478</v>
+        <v>-0.08506621150886014</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.07528214501248236</v>
+        <v>0.2533118520349926</v>
       </c>
       <c r="EU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.04506702486800113</v>
+        <v>-0.3035134126702108</v>
       </c>
       <c r="EZ8" t="n">
         <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.00546366305083414</v>
+        <v>0.06174690611041216</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.01438115218192496</v>
+        <v>-0.1258363676875327</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.04543062448445263</v>
+        <v>0.1005455295567257</v>
       </c>
       <c r="FD8" t="n">
         <v>0</v>
       </c>
       <c r="FE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.04039766155185378</v>
+        <v>-0.2252209711266066</v>
       </c>
       <c r="FI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.02983183999575903</v>
+        <v>0.1450059309370776</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.0007851676876486605</v>
+        <v>-0.05643216118085478</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.01433026219893621</v>
+        <v>0.3725972217875037</v>
       </c>
       <c r="FM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
         <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.008472526443757575</v>
+        <v>-0.1987113304785901</v>
       </c>
       <c r="FR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.009498651053461057</v>
+        <v>0.2872777944503768</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.004007978858819655</v>
+        <v>0.001955805748718278</v>
       </c>
       <c r="FU8" t="n">
-        <v>-0.0006667495878353233</v>
+        <v>0.09628168885746909</v>
       </c>
       <c r="FV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW8" t="n">
         <v>-0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.03059570853169198</v>
+        <v>-0.1150369726107396</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
-        <v>-0.02431450821081933</v>
+        <v>-0.1620036778414712</v>
       </c>
       <c r="GC8" t="n">
         <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.00280911641239717</v>
+        <v>-0.07776944272891266</v>
       </c>
       <c r="GE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5551,10 +5551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.6366712051656227</v>
+        <v>-0.2221806683100062</v>
       </c>
       <c r="C10" t="n">
         <v>-0</v>
@@ -5563,13 +5563,13 @@
         <v>-0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.08697509212496833</v>
+        <v>-0.00889114524676057</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9845505032661335</v>
+        <v>0.2071219026413123</v>
       </c>
       <c r="G10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -5578,10 +5578,10 @@
         <v>-0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2041022886760888</v>
+        <v>-0.08877588718342412</v>
       </c>
       <c r="L10" t="n">
         <v>-0</v>
@@ -5590,10 +5590,10 @@
         <v>-0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.07967963966601621</v>
+        <v>0.04478604186745562</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5597213971528552</v>
+        <v>0.1286645198798842</v>
       </c>
       <c r="P10" t="n">
         <v>-0</v>
@@ -5608,22 +5608,22 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.08715578462065252</v>
+        <v>-0.08966617172079253</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V10" t="n">
         <v>-0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1128410981611434</v>
+        <v>-0.008144594579350361</v>
       </c>
       <c r="X10" t="n">
-        <v>0.02691143437295237</v>
+        <v>-0.03370216851146943</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -5635,19 +5635,19 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.2329839477389476</v>
+        <v>0.06395419421672134</v>
       </c>
       <c r="AD10" t="n">
         <v>-0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.01763307552341737</v>
+        <v>0.1431213228712825</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.1836191853288344</v>
+        <v>0.03843540805456153</v>
       </c>
       <c r="AH10" t="n">
         <v>-0</v>
@@ -5662,22 +5662,22 @@
         <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.07512987684999103</v>
+        <v>-0.1195672020171534</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.135831083578605</v>
+        <v>-0.08110743673424843</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.2797066560146976</v>
+        <v>0.1499306681790015</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -5689,7 +5689,7 @@
         <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.3741165585892315</v>
+        <v>-0.2996360635293902</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -5698,25 +5698,25 @@
         <v>-0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.356610395667373</v>
+        <v>0.06957098589022027</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.9361587589155737</v>
+        <v>0.1315384260110089</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
         <v>-0</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.4424338738470506</v>
+        <v>0.1029697910086837</v>
       </c>
       <c r="BE10" t="n">
         <v>-0</v>
@@ -5725,25 +5725,25 @@
         <v>-0</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.1384431771571384</v>
+        <v>0.2152339857655745</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.1945064143017782</v>
+        <v>0.122901684707437</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>-0.1234283867715481</v>
+        <v>0.0289832139913838</v>
       </c>
       <c r="BN10" t="n">
         <v>0</v>
@@ -5752,10 +5752,10 @@
         <v>0</v>
       </c>
       <c r="BP10" t="n">
-        <v>-0.1181142808420209</v>
+        <v>-0.0555476991848121</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.01576618077189797</v>
+        <v>-0.0558477689995262</v>
       </c>
       <c r="BR10" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
         <v>0</v>
       </c>
       <c r="BV10" t="n">
-        <v>-0.1934659202605951</v>
+        <v>-0.2176631160389566</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
@@ -5779,16 +5779,16 @@
         <v>-0</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.08962884748241209</v>
+        <v>-0.006294189550604892</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.3651984907511022</v>
+        <v>0.08621590065375564</v>
       </c>
       <c r="CA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC10" t="n">
         <v>-0</v>
@@ -5797,7 +5797,7 @@
         <v>0</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.1955823356127975</v>
+        <v>0.1294020485609261</v>
       </c>
       <c r="CF10" t="n">
         <v>0</v>
@@ -5806,10 +5806,10 @@
         <v>0</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.00816970540163724</v>
+        <v>-0.01003754115683648</v>
       </c>
       <c r="CI10" t="n">
-        <v>-0.1995026485597582</v>
+        <v>-0.08062827819193177</v>
       </c>
       <c r="CJ10" t="n">
         <v>0</v>
@@ -5818,25 +5818,25 @@
         <v>-0</v>
       </c>
       <c r="CL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.01797619952919976</v>
+        <v>0.0754060753117639</v>
       </c>
       <c r="CO10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP10" t="n">
         <v>0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.2259606775065933</v>
+        <v>-0.1454528902636138</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.1226291382239544</v>
+        <v>-0.03863716173996184</v>
       </c>
       <c r="CS10" t="n">
         <v>0</v>
@@ -5848,10 +5848,10 @@
         <v>0</v>
       </c>
       <c r="CV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.1636802209639074</v>
+        <v>0.1215560049042346</v>
       </c>
       <c r="CX10" t="n">
         <v>-0</v>
@@ -5860,10 +5860,10 @@
         <v>-0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.05765584815094123</v>
+        <v>-0.005699454326810917</v>
       </c>
       <c r="DA10" t="n">
-        <v>-0.234270734790426</v>
+        <v>-0.07379426942348548</v>
       </c>
       <c r="DB10" t="n">
         <v>-0</v>
@@ -5878,61 +5878,61 @@
         <v>-0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.01350735563069386</v>
+        <v>-0.004458481497502783</v>
       </c>
       <c r="DG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH10" t="n">
         <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.2700888201685094</v>
+        <v>0.05275108982827627</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.03526955508469724</v>
+        <v>-0.007808168251972187</v>
       </c>
       <c r="DK10" t="n">
         <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.1382643363050792</v>
+        <v>0.01254057254252931</v>
       </c>
       <c r="DP10" t="n">
         <v>0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.1018153573042857</v>
+        <v>0.01051363869718424</v>
       </c>
       <c r="DS10" t="n">
-        <v>-0.06027366733264448</v>
+        <v>-0.03530514319996934</v>
       </c>
       <c r="DT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV10" t="n">
         <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.1310266696181392</v>
+        <v>-0.04886435877787023</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
@@ -5941,10 +5941,10 @@
         <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.3027254627391702</v>
+        <v>0.06151491881858998</v>
       </c>
       <c r="EB10" t="n">
-        <v>-0.1202720083068612</v>
+        <v>0.02188798943999884</v>
       </c>
       <c r="EC10" t="n">
         <v>0</v>
@@ -5953,25 +5953,25 @@
         <v>-0</v>
       </c>
       <c r="EE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF10" t="n">
         <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.08451005182699307</v>
+        <v>0.06679027795536686</v>
       </c>
       <c r="EH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>-0.1280852604447768</v>
+        <v>0.01562047184399274</v>
       </c>
       <c r="EK10" t="n">
-        <v>-0.1644445508303873</v>
+        <v>-0.009264715892268242</v>
       </c>
       <c r="EL10" t="n">
         <v>0</v>
@@ -5980,40 +5980,40 @@
         <v>-0</v>
       </c>
       <c r="EN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.1665701240754379</v>
+        <v>0.1033089678227893</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.08792102926841404</v>
+        <v>0.07747313116232407</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0.00308022753749505</v>
+        <v>0.0943310659010813</v>
       </c>
       <c r="EU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.177007614638068</v>
+        <v>0.1354671311481852</v>
       </c>
       <c r="EZ10" t="n">
         <v>0</v>
@@ -6022,10 +6022,10 @@
         <v>0</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.05603850867091844</v>
+        <v>0.0002291822268167367</v>
       </c>
       <c r="FC10" t="n">
-        <v>-0.2370799297251215</v>
+        <v>-0.06437560627687069</v>
       </c>
       <c r="FD10" t="n">
         <v>0</v>
@@ -6037,10 +6037,10 @@
         <v>0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.0140750532655642</v>
+        <v>0.1204245175631809</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
@@ -6049,37 +6049,37 @@
         <v>0</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.02253241486306879</v>
+        <v>-0.02566196495603158</v>
       </c>
       <c r="FL10" t="n">
-        <v>-0.252454003355767</v>
+        <v>-0.1077820240306862</v>
       </c>
       <c r="FM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN10" t="n">
         <v>-0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.0006296877171737042</v>
+        <v>0.1063617964989911</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
         <v>0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.1505408508105391</v>
+        <v>-0.008717879857046541</v>
       </c>
       <c r="FU10" t="n">
-        <v>-0.3471022743025425</v>
+        <v>-0.06736844530401781</v>
       </c>
       <c r="FV10" t="n">
         <v>0</v>
@@ -6094,10 +6094,10 @@
         <v>-0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.1318251794098035</v>
+        <v>0.1135241997632618</v>
       </c>
       <c r="GA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB10" t="n">
         <v>0</v>
@@ -6106,7 +6106,7 @@
         <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.07958104312441333</v>
+        <v>0.02004907915461063</v>
       </c>
       <c r="GE10" t="n">
         <v>0</v>
@@ -6120,22 +6120,22 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1318740611932359</v>
+        <v>0.5426926885220239</v>
       </c>
       <c r="C11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.005492943149031097</v>
+        <v>0.0216439644609442</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.09237698915256519</v>
+        <v>-0.2923418538645213</v>
       </c>
       <c r="G11" t="n">
         <v>-0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.09435844624903741</v>
+        <v>0.5661190309108086</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6159,16 +6159,16 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.00387433263232507</v>
+        <v>-0.09563749562748579</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.05231596628413955</v>
+        <v>-0.1732764805130526</v>
       </c>
       <c r="P11" t="n">
         <v>-0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>-0</v>
@@ -6177,7 +6177,7 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.008302545337658861</v>
+        <v>0.1397605311519744</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
@@ -6186,16 +6186,16 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.01636179756816476</v>
+        <v>0.01367648753741331</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.01620105783673412</v>
+        <v>-0.1497068214381005</v>
       </c>
       <c r="Y11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -6204,19 +6204,19 @@
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.007877545156851748</v>
+        <v>-0.003526613107522172</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.01256317973892767</v>
+        <v>-0.06849181379340162</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.01658887695230819</v>
+        <v>0.09935494307920836</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -6231,22 +6231,22 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.005307641575658446</v>
+        <v>0.1727523325470297</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.01050052098194327</v>
+        <v>0.06534458083560532</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.04321017063011174</v>
+        <v>-0.09377243243483918</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
@@ -6255,37 +6255,37 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.1082364385961864</v>
+        <v>0.7312310865990951</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.008984154601010062</v>
+        <v>-0.2731384405480271</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.06027269610127131</v>
+        <v>-0.2909331629523529</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA11" t="n">
         <v>-0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.05150394732376543</v>
+        <v>-0.1745625232477025</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,37 +6294,37 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.02408309547370742</v>
+        <v>0.005786022652157777</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.0588905221505984</v>
+        <v>-0.07462255900810361</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ11" t="n">
         <v>0</v>
       </c>
       <c r="BK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.04170675385584562</v>
+        <v>0.01556386561530482</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.0149431797754241</v>
+        <v>0.07798829561103375</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.01932360625396138</v>
+        <v>0.05339409097859832</v>
       </c>
       <c r="BR11" t="n">
         <v>0</v>
@@ -6333,13 +6333,13 @@
         <v>-0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.05519751872298534</v>
+        <v>0.4500287478261169</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,10 +6348,10 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.003424969247851455</v>
+        <v>-0.01561094248927397</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0.02183011723430995</v>
+        <v>-0.1659425329872808</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
@@ -6366,25 +6366,25 @@
         <v>0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.02931573640885643</v>
+        <v>-0.2468026572995994</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.002823752722626449</v>
+        <v>0.01019721401887829</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.02455424238017028</v>
+        <v>0.1116319612636757</v>
       </c>
       <c r="CJ11" t="n">
         <v>0</v>
       </c>
       <c r="CK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL11" t="n">
         <v>0</v>
@@ -6393,61 +6393,61 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.00837748048736099</v>
+        <v>-0.08906866487965028</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.003916928761573623</v>
+        <v>0.08918441836054587</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.008731407320691024</v>
+        <v>0.03077762234635981</v>
       </c>
       <c r="CS11" t="n">
         <v>-0</v>
       </c>
       <c r="CT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
         <v>-0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.02153164021549675</v>
+        <v>-0.2337639456815072</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.002003978309657736</v>
+        <v>0.01062951206723477</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.0303857761322393</v>
+        <v>0.1272685362638746</v>
       </c>
       <c r="DB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.004146839197418542</v>
+        <v>0.01319594562448032</v>
       </c>
       <c r="DG11" t="n">
         <v>0</v>
@@ -6456,10 +6456,10 @@
         <v>-0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.007833888145544933</v>
+        <v>0.01862450382195774</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.0131833482100878</v>
+        <v>0.1003835515782636</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
@@ -6471,28 +6471,28 @@
         <v>0</v>
       </c>
       <c r="DN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.01266161839795827</v>
+        <v>-0.07802572974572441</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.008747440187639103</v>
+        <v>-0.006917124975122394</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.004134410553009287</v>
+        <v>0.09378093681377034</v>
       </c>
       <c r="DT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
         <v>0</v>
@@ -6501,46 +6501,46 @@
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.03638192622515123</v>
+        <v>-0.1401538117322314</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.00969916336586552</v>
+        <v>0.0645073818154584</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0.01868138726598854</v>
+        <v>-0.1251596216932681</v>
       </c>
       <c r="EC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
         <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.02008322058823762</v>
+        <v>-0.141545844024727</v>
       </c>
       <c r="EH11" t="n">
         <v>-0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.002968698146550201</v>
+        <v>-0.0573144815104106</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.01589273350073591</v>
+        <v>0.03738375968993004</v>
       </c>
       <c r="EL11" t="n">
         <v>-0</v>
@@ -6555,19 +6555,19 @@
         <v>0</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.006071964025114669</v>
+        <v>0.1093431111161352</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
         <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.003405872680952868</v>
+        <v>0.01044666176605473</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.003510917546484083</v>
+        <v>-0.03806871826453082</v>
       </c>
       <c r="EU11" t="n">
         <v>0</v>
@@ -6576,58 +6576,58 @@
         <v>0</v>
       </c>
       <c r="EW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX11" t="n">
         <v>0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.02109768676030957</v>
+        <v>-0.2680743063443463</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.001335814361383439</v>
+        <v>-0.01515814202184137</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.03096725298424894</v>
+        <v>0.1231524119663395</v>
       </c>
       <c r="FD11" t="n">
         <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.004398873560933414</v>
+        <v>-0.140885186080247</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ11" t="n">
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.0162621825293441</v>
+        <v>-0.03966369495935109</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.02933338994252381</v>
+        <v>0.1121332542661675</v>
       </c>
       <c r="FM11" t="n">
         <v>-0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
@@ -6636,7 +6636,7 @@
         <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.02071820846187045</v>
+        <v>-0.2392300522857213</v>
       </c>
       <c r="FR11" t="n">
         <v>-0</v>
@@ -6645,37 +6645,37 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.02281204601385389</v>
+        <v>-0.07504610062722977</v>
       </c>
       <c r="FU11" t="n">
-        <v>-0.0008419326948454599</v>
+        <v>-0.006788029017868638</v>
       </c>
       <c r="FV11" t="n">
         <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
         <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.01337342822206208</v>
+        <v>-0.1129876723369952</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.02628249890962805</v>
+        <v>0.07090851134440188</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6684,7 +6684,7 @@
         <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,16 +6692,16 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.4203970612742267</v>
+        <v>-0.3902375468267102</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2381725178332416</v>
+        <v>0.1878473641023177</v>
       </c>
       <c r="E12" t="n">
-        <v>0.273264130438886</v>
+        <v>0.08867952594288413</v>
       </c>
       <c r="F12" t="n">
         <v>-0</v>
@@ -6710,28 +6710,28 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3101477086637015</v>
+        <v>-0.4286505831184733</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2222121562054488</v>
+        <v>0.2669801854041424</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2696280773763496</v>
+        <v>0.1405202464332765</v>
       </c>
       <c r="O12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -6746,127 +6746,127 @@
         <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1284318551118342</v>
+        <v>-0.04109162553456438</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.01904545226727132</v>
+        <v>0.01533178623558822</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.07335317270094205</v>
+        <v>-0.0116301129691597</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>-0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.1704161127400031</v>
+        <v>-0.03030981253780318</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.05715818951733054</v>
+        <v>0.153763654368942</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.02356619343079017</v>
+        <v>-0.2217726761944828</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.04896102394264443</v>
+        <v>-0.1440833969953473</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.04477912547546925</v>
+        <v>0.04284552320016726</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.07869489294520983</v>
+        <v>-0.2331040469144822</v>
       </c>
       <c r="AP12" t="n">
         <v>-0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR12" t="n">
         <v>-0</v>
       </c>
       <c r="AS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>-0.3401131025108767</v>
+        <v>-0.2425030489364495</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.06970047537053838</v>
+        <v>0.181064099648297</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.008627081229880568</v>
+        <v>0.04343781030329023</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
         <v>-0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.008829065649101577</v>
+        <v>0.03074010019572927</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.2161857308369209</v>
+        <v>0.01945866673344017</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.3428484569850302</v>
+        <v>0.09399341976463066</v>
       </c>
       <c r="BH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI12" t="n">
         <v>-0</v>
@@ -6881,16 +6881,16 @@
         <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>-0.09089568020081853</v>
+        <v>0.1097310862730086</v>
       </c>
       <c r="BN12" t="n">
         <v>0</v>
       </c>
       <c r="BO12" t="n">
-        <v>-0.02630949504052616</v>
+        <v>0.07264371408636869</v>
       </c>
       <c r="BP12" t="n">
-        <v>-0.09840232868604756</v>
+        <v>-0.01118954949787514</v>
       </c>
       <c r="BQ12" t="n">
         <v>0</v>
@@ -6908,25 +6908,25 @@
         <v>0</v>
       </c>
       <c r="BV12" t="n">
-        <v>-0.2637835255097385</v>
+        <v>-0.1862108689479959</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.005855053553077499</v>
+        <v>0.08266163169074263</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.04968715169096643</v>
+        <v>0.0009322462403479262</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC12" t="n">
         <v>-0</v>
@@ -6935,16 +6935,16 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.0994917647820658</v>
+        <v>0.1947108411207845</v>
       </c>
       <c r="CF12" t="n">
         <v>0</v>
       </c>
       <c r="CG12" t="n">
-        <v>-0.05981657916910861</v>
+        <v>-0.06887845048790521</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.001654412517811515</v>
+        <v>-0.01049244579751373</v>
       </c>
       <c r="CI12" t="n">
         <v>0</v>
@@ -6962,19 +6962,19 @@
         <v>-0</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.03904433531414777</v>
+        <v>0.09077372166627176</v>
       </c>
       <c r="CO12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.08836504795522895</v>
+        <v>-0.08014811475072159</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.08395989053667714</v>
+        <v>-0.02544203126988138</v>
       </c>
       <c r="CR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS12" t="n">
         <v>0</v>
@@ -6989,46 +6989,46 @@
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.09909492014780513</v>
+        <v>0.2097527983783143</v>
       </c>
       <c r="CX12" t="n">
         <v>-0</v>
       </c>
       <c r="CY12" t="n">
-        <v>-0.08172709137269067</v>
+        <v>-0.0736227543940539</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.01289019254973816</v>
+        <v>-0.0364095225089445</v>
       </c>
       <c r="DA12" t="n">
         <v>-0</v>
       </c>
       <c r="DB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD12" t="n">
         <v>-0</v>
       </c>
       <c r="DE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.1913335792505671</v>
+        <v>0.1500866290529764</v>
       </c>
       <c r="DG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0.09039708995659418</v>
+        <v>-0.0391471973239022</v>
       </c>
       <c r="DI12" t="n">
-        <v>-0.01612744328293991</v>
+        <v>0.0004639762198912587</v>
       </c>
       <c r="DJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK12" t="n">
         <v>0</v>
@@ -7037,25 +7037,25 @@
         <v>-0</v>
       </c>
       <c r="DM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.05315386549332303</v>
+        <v>0.09944575259077537</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.03945751839556569</v>
+        <v>-0.07080232137162867</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.07524115673016218</v>
+        <v>0.04003092691685088</v>
       </c>
       <c r="DS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT12" t="n">
         <v>0</v>
@@ -7070,22 +7070,22 @@
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.1090832463548563</v>
+        <v>0.04319991691164538</v>
       </c>
       <c r="DY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.1120631691043394</v>
+        <v>0.02552862267756187</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.04292370431063442</v>
+        <v>0.003611966123300141</v>
       </c>
       <c r="EB12" t="n">
         <v>0</v>
       </c>
       <c r="EC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED12" t="n">
         <v>-0</v>
@@ -7097,25 +7097,25 @@
         <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.06261320051121112</v>
+        <v>0.2200148816607372</v>
       </c>
       <c r="EH12" t="n">
         <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>-0.05128472242952131</v>
+        <v>-0.0515402049540205</v>
       </c>
       <c r="EJ12" t="n">
-        <v>-0.1280042182459941</v>
+        <v>-0.04497360168235492</v>
       </c>
       <c r="EK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN12" t="n">
         <v>0</v>
@@ -7124,25 +7124,25 @@
         <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.01090740335426707</v>
+        <v>-0.1175512243664153</v>
       </c>
       <c r="EQ12" t="n">
         <v>0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.03305469095304838</v>
+        <v>-0.01124282473495074</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.02963720384945741</v>
+        <v>0.01338937614481888</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
         <v>-0</v>
       </c>
       <c r="EV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW12" t="n">
         <v>0</v>
@@ -7151,16 +7151,16 @@
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.1021779611874328</v>
+        <v>0.2340009828994381</v>
       </c>
       <c r="EZ12" t="n">
         <v>0</v>
       </c>
       <c r="FA12" t="n">
-        <v>-0.07113789239965995</v>
+        <v>-0.0846230944567089</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.01393453093228759</v>
+        <v>-0.007484793920215041</v>
       </c>
       <c r="FC12" t="n">
         <v>0</v>
@@ -7169,52 +7169,52 @@
         <v>-0</v>
       </c>
       <c r="FE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.07244239177882095</v>
+        <v>0.08649804043931243</v>
       </c>
       <c r="FI12" t="n">
         <v>0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.1034012052979759</v>
+        <v>0.09156880849337438</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.05343306529002467</v>
+        <v>0.02003220934353154</v>
       </c>
       <c r="FL12" t="n">
         <v>0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.01786479763664515</v>
+        <v>0.1824214370626203</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.03866397923095361</v>
+        <v>0.01471591573657509</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.003043364984106816</v>
+        <v>-0.08443438783763341</v>
       </c>
       <c r="FU12" t="n">
         <v>0</v>
@@ -7223,37 +7223,37 @@
         <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX12" t="n">
         <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.06642362777887707</v>
+        <v>0.1962122176105751</v>
       </c>
       <c r="GA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.06278896293088311</v>
+        <v>-0.005883491887675817</v>
       </c>
       <c r="GC12" t="n">
         <v>-0</v>
       </c>
       <c r="GD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE12" t="n">
         <v>0</v>
       </c>
       <c r="GF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4944175880602533</v>
+        <v>0.3673263660664046</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,16 +7270,16 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1198894349094563</v>
+        <v>-0.03132362115763966</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4544460008606231</v>
+        <v>-0.1574310961824845</v>
       </c>
       <c r="G13" t="n">
         <v>-0</v>
       </c>
       <c r="H13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -7288,7 +7288,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4274607518904434</v>
+        <v>0.4485034714310024</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -7297,25 +7297,25 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.04888874850773579</v>
+        <v>-0.130178196493785</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4157528138401824</v>
+        <v>-0.1955038102499164</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.04063933094066322</v>
+        <v>0.1181387580374067</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -7324,16 +7324,16 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.08967454752124288</v>
+        <v>-0.1505967697670783</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.01598316809495008</v>
+        <v>-0.008656607559602366</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -7342,19 +7342,19 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.02252847513618931</v>
+        <v>-0.03162450802245122</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.008390708569729568</v>
+        <v>-0.2887825223557907</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.03544500394326719</v>
+        <v>0.003527479040623809</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7369,7 +7369,7 @@
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.08318877872611036</v>
+        <v>0.04767021123248868</v>
       </c>
       <c r="AM13" t="n">
         <v>-0</v>
@@ -7378,10 +7378,10 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.0007077278191615895</v>
+        <v>-0.05554508401760289</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.08540701532056351</v>
+        <v>0.01816034171727798</v>
       </c>
       <c r="AQ13" t="n">
         <v>-0</v>
@@ -7393,10 +7393,10 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.4218259438604975</v>
+        <v>0.5191454181042116</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
@@ -7405,16 +7405,16 @@
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.06897385573744649</v>
+        <v>-0.2773316772019603</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.2205919160920708</v>
+        <v>-0.1188790333326577</v>
       </c>
       <c r="AZ13" t="n">
         <v>-0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>0</v>
@@ -7423,7 +7423,7 @@
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.1099878069610339</v>
+        <v>-0.04339056641769333</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,52 +7432,52 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.1555668212240102</v>
+        <v>-0.02496902837454742</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.2031233903851091</v>
+        <v>-0.08294885925804485</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.1451342674025795</v>
+        <v>0.05824419041574769</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>-0.002556688646453596</v>
+        <v>0.08937834520485273</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.0211355153587851</v>
+        <v>-0.02766133106619291</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.2207219932939731</v>
+        <v>0.280554085961145</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
@@ -7486,10 +7486,10 @@
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.06717633274302381</v>
+        <v>-0.08484454530252006</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.129854641674758</v>
+        <v>-0.1133443628907627</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
@@ -7504,22 +7504,22 @@
         <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.08697241061607046</v>
+        <v>-0.1241005857088528</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.005260933946613045</v>
+        <v>0.02982513345676222</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.1102993405917673</v>
+        <v>0.05788680263723674</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
@@ -7531,49 +7531,49 @@
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-4.43257607350541e-05</v>
+        <v>-0.1130418455220918</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.01466065102031537</v>
+        <v>0.1111120639927183</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.02412898156694127</v>
+        <v>0.09855759559282742</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV13" t="n">
         <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.0687753690642883</v>
+        <v>-0.1207477986492186</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.001385798239291539</v>
+        <v>0.00912079538591205</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.1157981227674384</v>
+        <v>0.0813693175712514</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
         <v>-0</v>
@@ -7585,25 +7585,25 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.04431739291869521</v>
+        <v>-0.0540124289549061</v>
       </c>
       <c r="DG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.0469190519338525</v>
+        <v>-0.1975404969883628</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.0004228659813447472</v>
+        <v>0.07982109192302066</v>
       </c>
       <c r="DK13" t="n">
         <v>0</v>
       </c>
       <c r="DL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM13" t="n">
         <v>0</v>
@@ -7612,19 +7612,19 @@
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.006641109162840441</v>
+        <v>-0.02073396924641933</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.03409219115504388</v>
+        <v>-0.06329309576383095</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0.007839961212285225</v>
+        <v>0.08041025222081968</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
@@ -7633,13 +7633,13 @@
         <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.05630551712360807</v>
+        <v>-0.0268568656386304</v>
       </c>
       <c r="DY13" t="n">
         <v>0</v>
@@ -7648,25 +7648,25 @@
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.01739268735557954</v>
+        <v>-0.0550253324327012</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.05349210144062201</v>
+        <v>0.04359670920676496</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
         <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.1002099334802206</v>
+        <v>-0.05013198736437276</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
@@ -7675,79 +7675,79 @@
         <v>-0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.02829821554655291</v>
+        <v>0.01336142295899115</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.1234794527568776</v>
+        <v>-0.006961048616991997</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
         <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.03354367535041377</v>
+        <v>-0.01249802592186753</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.01138240262551658</v>
+        <v>-0.005899383144940205</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.07389758701291133</v>
+        <v>0.1446168996258657</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
         <v>0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
         <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.06650577815978947</v>
+        <v>-0.1419693449424611</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.00686835868898876</v>
+        <v>-0.0004515334052908549</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.1058259541203652</v>
+        <v>0.04850484575129888</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.005797606991718213</v>
+        <v>0.2021335913128045</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
@@ -7756,16 +7756,16 @@
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.008269053209006944</v>
+        <v>-0.07289011355661995</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.05044232467575337</v>
+        <v>0.1309518990581542</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
         <v>0</v>
@@ -7774,46 +7774,46 @@
         <v>0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.005420703803291718</v>
+        <v>0.008538417899239708</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.008628367138022312</v>
+        <v>-0.02237659527608413</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.03001674149327355</v>
+        <v>-0.04848437542451323</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.04279250744070507</v>
+        <v>-0.03346134264582198</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.05313188342164341</v>
+        <v>0.08115448268945702</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
@@ -7822,7 +7822,7 @@
         <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -8968,7 +8968,7 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1465852228526663</v>
+        <v>0.3969256418546411</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -8977,25 +8977,25 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.07399542798630397</v>
+        <v>-0.01718061647502239</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0709790340585276</v>
+        <v>-0.1595186744597766</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1108856173884611</v>
+        <v>0.4372282952607412</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -9004,25 +9004,25 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.04595669083434802</v>
+        <v>-0.1139331941005722</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.06470193804116534</v>
+        <v>-0.1912269917031652</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.01286623979709052</v>
+        <v>0.1044942959889899</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -9031,40 +9031,40 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.006100835549428585</v>
+        <v>-0.09466072415932646</v>
       </c>
       <c r="X16" t="n">
-        <v>0.009342836230473214</v>
+        <v>-0.02024099506776598</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.004928984544738137</v>
+        <v>-0.03685664010370459</v>
       </c>
       <c r="AD16" t="n">
         <v>-0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.01258156439247423</v>
+        <v>-0.2552359378293638</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.01050107998378377</v>
+        <v>0.045977414084051</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI16" t="n">
         <v>-0</v>
@@ -9076,22 +9076,22 @@
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.009158633067053728</v>
+        <v>0.04261947115897059</v>
       </c>
       <c r="AM16" t="n">
         <v>-0</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.009344143710511673</v>
+        <v>-0.03674726705645801</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.01452169277157193</v>
+        <v>0.004084694325702766</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
         <v>-0</v>
@@ -9100,28 +9100,28 @@
         <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.1019198328055797</v>
+        <v>0.4298116403776999</v>
       </c>
       <c r="AV16" t="n">
         <v>-0</v>
       </c>
       <c r="AW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>-0.02807047747016878</v>
+        <v>-0.266703631100383</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0.02016552463268135</v>
+        <v>-0.1209157629426972</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
         <v>0</v>
@@ -9130,7 +9130,7 @@
         <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.03040979956368515</v>
+        <v>-0.01793593956142691</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
@@ -9139,52 +9139,52 @@
         <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.05200338909831748</v>
+        <v>-0.006101564241852741</v>
       </c>
       <c r="BH16" t="n">
-        <v>-0.06011200255662029</v>
+        <v>-0.06069118740482153</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
         <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.03426528983123459</v>
+        <v>0.05052678002126591</v>
       </c>
       <c r="BN16" t="n">
         <v>-0</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.01557273011220122</v>
+        <v>0.06157330246901688</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.01534036555480199</v>
+        <v>-0.01112595399125816</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
         <v>-0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.047368182566852</v>
+        <v>0.2414822798158145</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
@@ -9193,10 +9193,10 @@
         <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.01165554142871243</v>
+        <v>-0.05985773466473071</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0.01167342535910132</v>
+        <v>-0.1240202384482711</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
@@ -9208,28 +9208,28 @@
         <v>-0</v>
       </c>
       <c r="CD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.02434920044063748</v>
+        <v>-0.1137540148714066</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
         <v>-0</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.006277110844750866</v>
+        <v>0.02917904079566028</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.01747917093761229</v>
+        <v>0.05963678913299981</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL16" t="n">
         <v>0</v>
@@ -9238,7 +9238,7 @@
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.0008711438210970087</v>
+        <v>-0.1147816444000389</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
@@ -9247,97 +9247,97 @@
         <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.004870258777359961</v>
+        <v>0.1496826747591614</v>
       </c>
       <c r="CR16" t="n">
-        <v>-0.01055356244104783</v>
+        <v>0.06868932225718427</v>
       </c>
       <c r="CS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT16" t="n">
         <v>0</v>
       </c>
       <c r="CU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV16" t="n">
         <v>-0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.01837875031968109</v>
+        <v>-0.1119537330061609</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.005788378002291633</v>
+        <v>0.01827083508161986</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.01825785415799794</v>
+        <v>0.08222235311554203</v>
       </c>
       <c r="DB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.03055706956215015</v>
+        <v>-0.07805895886511502</v>
       </c>
       <c r="DG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.04795676047248516</v>
+        <v>-0.2053762820890815</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.01313787130993649</v>
+        <v>0.06667956780340208</v>
       </c>
       <c r="DK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL16" t="n">
         <v>-0</v>
       </c>
       <c r="DM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.004916013979101529</v>
+        <v>-0.009997958543084565</v>
       </c>
       <c r="DP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ16" t="n">
         <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.01919661233951572</v>
+        <v>-0.06021135600141588</v>
       </c>
       <c r="DS16" t="n">
-        <v>-0.007774198957988798</v>
+        <v>0.04169724196238191</v>
       </c>
       <c r="DT16" t="n">
         <v>-0</v>
       </c>
       <c r="DU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV16" t="n">
         <v>-0</v>
@@ -9346,49 +9346,49 @@
         <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.02846097191678534</v>
+        <v>-0.005631911990851824</v>
       </c>
       <c r="DY16" t="n">
         <v>0</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.01360604075316584</v>
+        <v>-0.03638945139055259</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.01789462456361692</v>
+        <v>0.01366938329681499</v>
       </c>
       <c r="EC16" t="n">
         <v>-0</v>
       </c>
       <c r="ED16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.02911864151567194</v>
+        <v>-0.05787979272810461</v>
       </c>
       <c r="EH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.008480714679931127</v>
+        <v>0.01772311591468043</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.01387669463880132</v>
+        <v>0.002135051693077886</v>
       </c>
       <c r="EL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM16" t="n">
         <v>-0</v>
@@ -9397,22 +9397,22 @@
         <v>-0</v>
       </c>
       <c r="EO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.01260822431150292</v>
+        <v>-0.03440564933223574</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.003845554478425642</v>
+        <v>-0.01208967426754717</v>
       </c>
       <c r="ET16" t="n">
-        <v>-0.01036215508293767</v>
+        <v>0.1090035198219108</v>
       </c>
       <c r="EU16" t="n">
         <v>0</v>
@@ -9421,58 +9421,58 @@
         <v>0</v>
       </c>
       <c r="EW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.01930000018848992</v>
+        <v>-0.1301528791426035</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.008683513147103507</v>
+        <v>0.002589470299987057</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.02122334911163535</v>
+        <v>0.04926107642619053</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
         <v>-0</v>
       </c>
       <c r="FF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG16" t="n">
         <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.01604457638516874</v>
+        <v>0.1839387303034509</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ16" t="n">
         <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.01197799151554985</v>
+        <v>-0.07780575109705781</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.01949669269291303</v>
+        <v>0.1383156177246908</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO16" t="n">
         <v>0</v>
@@ -9481,78 +9481,78 @@
         <v>0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.0001186836000044023</v>
+        <v>0.002269034342212356</v>
       </c>
       <c r="FR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS16" t="n">
         <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.001333692896077636</v>
+        <v>-0.009107064464106952</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.0182015524807463</v>
+        <v>-0.03162385840654541</v>
       </c>
       <c r="FV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.0001952809621877177</v>
+        <v>-0.040712622699525</v>
       </c>
       <c r="GA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB16" t="n">
         <v>-0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0.00411468136418883</v>
+        <v>0.0758062636767521</v>
       </c>
       <c r="GE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF16" t="n">
         <v>-0</v>
       </c>
       <c r="GG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-0.8502837428435279</v>
+        <v>-0.2632674171497739</v>
       </c>
       <c r="B17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.05655871633976203</v>
+        <v>0.209488579268205</v>
       </c>
       <c r="F17" t="n">
-        <v>1.687231382981478</v>
+        <v>0.6283093612791977</v>
       </c>
       <c r="G17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -9561,22 +9561,22 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4323332666266763</v>
+        <v>-0.16441393391849</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L17" t="n">
         <v>-0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1602354216972428</v>
+        <v>0.3905909750829961</v>
       </c>
       <c r="O17" t="n">
-        <v>1.278894506970289</v>
+        <v>1.067381410106608</v>
       </c>
       <c r="P17" t="n">
         <v>-0</v>
@@ -9588,52 +9588,52 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1922866802710226</v>
+        <v>0.08536340758348407</v>
       </c>
       <c r="T17" t="n">
         <v>-0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V17" t="n">
         <v>-0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5082619239813235</v>
+        <v>-0.02150163681497325</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1915377317545275</v>
+        <v>0.128464423379295</v>
       </c>
       <c r="Y17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0.2231365369000803</v>
+        <v>-0.1540701535566233</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
         <v>-0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.1062409241909324</v>
+        <v>0.02410445369008753</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.09126751785465746</v>
+        <v>-0.3189598640268801</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -9642,7 +9642,7 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>-0.1899579490643113</v>
+        <v>-0.08704243343982818</v>
       </c>
       <c r="AL17" t="n">
         <v>-0</v>
@@ -9654,10 +9654,10 @@
         <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.01888882982903044</v>
+        <v>-0.3521654900326996</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.06123801101473281</v>
+        <v>-0.02474078680267843</v>
       </c>
       <c r="AQ17" t="n">
         <v>0</v>
@@ -9666,52 +9666,52 @@
         <v>-0</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT17" t="n">
-        <v>-0.6097803001632807</v>
+        <v>-0.02157083022841234</v>
       </c>
       <c r="AU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.6201411756746733</v>
+        <v>-0.2630871735945537</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.052831566551708</v>
+        <v>0.6539432702725795</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>-0.2060866365751479</v>
+        <v>-0.1945146997898888</v>
       </c>
       <c r="BD17" t="n">
         <v>-0</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.1354846950335468</v>
+        <v>0.5691703431710214</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.1952686044250534</v>
+        <v>-0.3498127435036994</v>
       </c>
       <c r="BI17" t="n">
         <v>-0</v>
@@ -9723,10 +9723,10 @@
         <v>0</v>
       </c>
       <c r="BL17" t="n">
-        <v>-0.03870840396197738</v>
+        <v>0.1527822424762326</v>
       </c>
       <c r="BM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN17" t="n">
         <v>0</v>
@@ -9735,40 +9735,40 @@
         <v>-0</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.06466038365058653</v>
+        <v>0.03445941759659151</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.1143795097060027</v>
+        <v>0.02567225477356964</v>
       </c>
       <c r="BR17" t="n">
         <v>0</v>
       </c>
       <c r="BS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT17" t="n">
         <v>-0</v>
       </c>
       <c r="BU17" t="n">
-        <v>-0.4089227988679115</v>
+        <v>-0.01203677852762843</v>
       </c>
       <c r="BV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.3257989605731144</v>
+        <v>-0.04024737753969684</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.6145798994091752</v>
+        <v>0.3525289303833425</v>
       </c>
       <c r="CA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB17" t="n">
         <v>-0</v>
@@ -9777,7 +9777,7 @@
         <v>-0</v>
       </c>
       <c r="CD17" t="n">
-        <v>0.2339331298305126</v>
+        <v>0.07345054580648686</v>
       </c>
       <c r="CE17" t="n">
         <v>-0</v>
@@ -9789,22 +9789,22 @@
         <v>-0</v>
       </c>
       <c r="CH17" t="n">
-        <v>-0.03677137526617377</v>
+        <v>-0.04725116843565927</v>
       </c>
       <c r="CI17" t="n">
-        <v>-0.3353032623842591</v>
+        <v>-0.06039160539440133</v>
       </c>
       <c r="CJ17" t="n">
         <v>-0</v>
       </c>
       <c r="CK17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL17" t="n">
         <v>-0</v>
       </c>
       <c r="CM17" t="n">
-        <v>-0.01918928072767162</v>
+        <v>-0.0775998314595973</v>
       </c>
       <c r="CN17" t="n">
         <v>0</v>
@@ -9816,25 +9816,25 @@
         <v>-0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.5706829987925043</v>
+        <v>-0.19300799013398</v>
       </c>
       <c r="CR17" t="n">
-        <v>-0.08236883473748149</v>
+        <v>0.270372402189268</v>
       </c>
       <c r="CS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV17" t="n">
-        <v>0.2203005068442297</v>
+        <v>0.08847749042046107</v>
       </c>
       <c r="CW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX17" t="n">
         <v>-0</v>
@@ -9843,10 +9843,10 @@
         <v>0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>-0.03393527105203356</v>
+        <v>-0.1431402407705024</v>
       </c>
       <c r="DA17" t="n">
-        <v>-0.3184503568692622</v>
+        <v>-0.1493073813460601</v>
       </c>
       <c r="DB17" t="n">
         <v>0</v>
@@ -9855,64 +9855,64 @@
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE17" t="n">
-        <v>-0.001021463966942377</v>
+        <v>0.005702698874129549</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0.4784050070619013</v>
+        <v>0.1655221300707579</v>
       </c>
       <c r="DJ17" t="n">
-        <v>-0.04168057656363482</v>
+        <v>-0.1487924714087882</v>
       </c>
       <c r="DK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL17" t="n">
         <v>-0</v>
       </c>
       <c r="DM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.1183995626040507</v>
+        <v>0.02059958295346414</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP17" t="n">
         <v>-0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR17" t="n">
-        <v>-0.1265712080371372</v>
+        <v>0.1345543001457302</v>
       </c>
       <c r="DS17" t="n">
-        <v>-0.09133203575488023</v>
+        <v>-0.1932710553984657</v>
       </c>
       <c r="DT17" t="n">
         <v>0</v>
       </c>
       <c r="DU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV17" t="n">
         <v>0</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.05651170388601569</v>
+        <v>0.06870129930356661</v>
       </c>
       <c r="DX17" t="n">
         <v>-0</v>
@@ -9921,43 +9921,43 @@
         <v>0</v>
       </c>
       <c r="DZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.02092785148218939</v>
+        <v>-0.1085888242326713</v>
       </c>
       <c r="EB17" t="n">
-        <v>-0.4458962471348428</v>
+        <v>-0.2807577804850698</v>
       </c>
       <c r="EC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED17" t="n">
         <v>-0</v>
       </c>
       <c r="EE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0.150650987458159</v>
+        <v>-0.05828302996004474</v>
       </c>
       <c r="EG17" t="n">
         <v>-0</v>
       </c>
       <c r="EH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI17" t="n">
         <v>-0</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.1534375046047704</v>
+        <v>-0.1747669799486979</v>
       </c>
       <c r="EK17" t="n">
-        <v>-0.2033266677291174</v>
+        <v>-0.06677483701364652</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
         <v>-0</v>
@@ -9966,7 +9966,7 @@
         <v>-0</v>
       </c>
       <c r="EO17" t="n">
-        <v>0.08454460904624655</v>
+        <v>0.02145072903661248</v>
       </c>
       <c r="EP17" t="n">
         <v>-0</v>
@@ -9978,10 +9978,10 @@
         <v>-0</v>
       </c>
       <c r="ES17" t="n">
-        <v>-0.3250134762032604</v>
+        <v>-0.09520561870017522</v>
       </c>
       <c r="ET17" t="n">
-        <v>-0.06627756881633352</v>
+        <v>-0.1823384893688573</v>
       </c>
       <c r="EU17" t="n">
         <v>-0</v>
@@ -9990,10 +9990,10 @@
         <v>-0</v>
       </c>
       <c r="EW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX17" t="n">
-        <v>0.187822665324337</v>
+        <v>0.04976585726261427</v>
       </c>
       <c r="EY17" t="n">
         <v>-0</v>
@@ -10005,94 +10005,94 @@
         <v>-0</v>
       </c>
       <c r="FB17" t="n">
-        <v>-0.08804884683926674</v>
+        <v>-0.04071157965018422</v>
       </c>
       <c r="FC17" t="n">
-        <v>-0.2809320706643329</v>
+        <v>-0.1488192175556596</v>
       </c>
       <c r="FD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG17" t="n">
-        <v>-0.09838211950112487</v>
+        <v>-0.1582405464879239</v>
       </c>
       <c r="FH17" t="n">
         <v>0</v>
       </c>
       <c r="FI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.08654835641166246</v>
+        <v>-0.06669776593887092</v>
       </c>
       <c r="FL17" t="n">
-        <v>-0.003487209481427227</v>
+        <v>-0.2664089717302998</v>
       </c>
       <c r="FM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP17" t="n">
-        <v>0.02852771258249955</v>
+        <v>0.02585028793104953</v>
       </c>
       <c r="FQ17" t="n">
         <v>0</v>
       </c>
       <c r="FR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS17" t="n">
         <v>-0</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.004379587628498551</v>
+        <v>0.001954674052398164</v>
       </c>
       <c r="FU17" t="n">
-        <v>-0.3123973185146371</v>
+        <v>-0.09633217170277589</v>
       </c>
       <c r="FV17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX17" t="n">
         <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0.09610245220745987</v>
+        <v>-0.1617989115940726</v>
       </c>
       <c r="FZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0.05448303746657592</v>
+        <v>-0.09756517395285559</v>
       </c>
       <c r="GE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF17" t="n">
         <v>-0</v>
